--- a/chemistry_book/content/project_THe/Orchestra_Project/tmp/df_work_PP-11N_converted_Orchestra_input.xlsx
+++ b/chemistry_book/content/project_THe/Orchestra_Project/tmp/df_work_PP-11N_converted_Orchestra_input.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Leachate_Sample" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Input_dat" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
   <si>
     <t xml:space="preserve">compartment</t>
   </si>
@@ -162,6 +163,33 @@
   </si>
   <si>
     <t xml:space="preserve">Var:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixed_logact_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar[g].logact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fe+2.tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mn+2.tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni+2.tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn+2.tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">watervolume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gasvolume</t>
   </si>
   <si>
     <t xml:space="preserve">Default:</t>
@@ -260,16 +288,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -293,34 +325,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -468,475 +500,475 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="25.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>410</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="0" t="n">
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>0.0102295409181637</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>0.029</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="0" t="n">
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>3.87079551521623E-007</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>4.2</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>7.52014324082364E-005</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>2600</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.042608980662078</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>3.74181478016838E-006</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>7.49261315942403</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="F7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>7.88945262653894E-005</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>1.8201674554059E-005</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>372.31884057971</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>0.0206385166618465</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="0" t="n">
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>0.00493624023035788</v>
       </c>
-      <c r="H10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.0051150895140665</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>15.9</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="0" t="n">
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>0.000566037735849057</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="F13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>0.0104372355430183</v>
       </c>
-      <c r="H13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="0" t="n">
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>0.0173988690735102</v>
       </c>
-      <c r="H14" s="0" t="s">
+      <c r="H14" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>0.027</v>
       </c>
-      <c r="F15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="0" t="n">
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>4.12970327317222E-007</v>
       </c>
-      <c r="H15" s="0" t="s">
+      <c r="H15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="F16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="0" t="n">
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>2.55580166979042E-007</v>
       </c>
-      <c r="H16" s="0" t="s">
+      <c r="H16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>7.16</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>7.16</v>
       </c>
-      <c r="H17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45272</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>769.625701809108</v>
       </c>
-      <c r="F18" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="0" t="n">
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>0.00801192693950768</v>
       </c>
-      <c r="H18" s="0" t="s">
+      <c r="H18" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -956,211 +988,469 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="W3" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>-11</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>3.870796E-007</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0.01022954</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.01043724</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>7.520143E-005</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0.04260898</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0.00511509</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0.00493624</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>1.820167E-005</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0.02063852</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>0.01739887</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>2.555802E-007</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>7.889453E-005</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>3.741815E-006</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>0.008011927</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>0.0005660377</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>4.129703E-007</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="U4" s="0" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="V4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>-11</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>3.870796E-007</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0.01022954</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0.01043724</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>7.520143E-005</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0.04260898</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0.00511509</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0.00493624</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>1.820167E-005</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0.02063852</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>0.01739887</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>2.555802E-007</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>7.889453E-005</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>3.741815E-006</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>0.008011927</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>0.0005660377</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>4.129703E-007</v>
+      </c>
+      <c r="T5" s="0" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="V5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1E-020</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="B1" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>44</v>
+      <c r="B3" s="0" t="n">
+        <v>3.870796E-007</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.0102295409181637</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>3.87079551521623E-007</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>7.52014324082364E-005</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>0.042608980662078</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>3.74181478016838E-006</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>7.88945262653894E-005</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>1.8201674554059E-005</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>0.0206385166618465</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>0.00493624023035788</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0.0051150895140665</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>0.000566037735849057</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <v>0.0104372355430183</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <v>0.0173988690735102</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <v>4.12970327317222E-007</v>
-      </c>
-      <c r="P4" s="0" t="n">
-        <v>2.55580166979042E-007</v>
-      </c>
-      <c r="Q4" s="0" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="R4" s="0" t="n">
-        <v>0.00801192693950768</v>
+        <v>0.01022954</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.0102295409181637</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>3.87079551521623E-007</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>7.52014324082364E-005</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0.042608980662078</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>3.74181478016838E-006</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>7.88945262653894E-005</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>1.8201674554059E-005</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>0.0206385166618465</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>0.00493624023035788</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0.0051150895140665</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>0.000566037735849057</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <v>0.0104372355430183</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <v>0.0173988690735102</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <v>4.12970327317222E-007</v>
-      </c>
-      <c r="P5" s="0" t="n">
-        <v>2.55580166979042E-007</v>
-      </c>
-      <c r="Q5" s="0" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="R5" s="0" t="n">
-        <v>0.00801192693950768</v>
+        <v>0.01043724</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>7.520143E-005</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.04260898</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>49</v>
+        <v>30</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.00511509</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.00493624</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>50</v>
       </c>
+      <c r="B10" s="0" t="n">
+        <v>1.820167E-005</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0.02063852</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.01739887</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="B13" s="0" t="n">
+        <v>2.555802E-007</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>7.889453E-005</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>3.741815E-006</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>0.008011927</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>0.0005660377</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>1E-020</v>
-      </c>
-      <c r="E11" s="0" t="n">
+      <c r="B18" s="0" t="n">
+        <v>4.129703E-007</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>291.75</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
